--- a/AAII_Financials/Yearly/MOTNF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOTNF_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -720,7 +720,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="3">
-        <v>20100</v>
+        <v>20300</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>4200</v>
       </c>
       <c r="E14" s="3">
-        <v>91100</v>
+        <v>92000</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="F15" s="3">
         <v>700</v>
@@ -920,19 +920,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13400</v>
+        <v>13600</v>
       </c>
       <c r="E17" s="3">
-        <v>158600</v>
+        <v>160200</v>
       </c>
       <c r="F17" s="3">
-        <v>42500</v>
+        <v>42900</v>
       </c>
       <c r="G17" s="3">
-        <v>67100</v>
+        <v>67800</v>
       </c>
       <c r="H17" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="I17" s="3">
         <v>300</v>
@@ -959,7 +959,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="3">
-        <v>14800</v>
+        <v>14900</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
@@ -1068,19 +1068,19 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E23" s="3">
-        <v>-160000</v>
+        <v>-161600</v>
       </c>
       <c r="F23" s="3">
-        <v>-42200</v>
+        <v>-42600</v>
       </c>
       <c r="G23" s="3">
-        <v>-67000</v>
+        <v>-67700</v>
       </c>
       <c r="H23" s="3">
-        <v>14800</v>
+        <v>14900</v>
       </c>
       <c r="I23" s="3">
         <v>-500</v>
@@ -1104,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-7300</v>
+        <v>-7400</v>
       </c>
       <c r="H24" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1149,16 +1149,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E26" s="3">
-        <v>-160000</v>
+        <v>-161600</v>
       </c>
       <c r="F26" s="3">
-        <v>-42200</v>
+        <v>-42600</v>
       </c>
       <c r="G26" s="3">
-        <v>-59700</v>
+        <v>-60300</v>
       </c>
       <c r="H26" s="3">
         <v>7500</v>
@@ -1176,16 +1176,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E27" s="3">
-        <v>-160000</v>
+        <v>-161600</v>
       </c>
       <c r="F27" s="3">
-        <v>-42200</v>
+        <v>-42600</v>
       </c>
       <c r="G27" s="3">
-        <v>-59700</v>
+        <v>-60300</v>
       </c>
       <c r="H27" s="3">
         <v>7500</v>
@@ -1338,16 +1338,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E33" s="3">
-        <v>-160000</v>
+        <v>-161600</v>
       </c>
       <c r="F33" s="3">
-        <v>-42200</v>
+        <v>-42600</v>
       </c>
       <c r="G33" s="3">
-        <v>-59700</v>
+        <v>-60300</v>
       </c>
       <c r="H33" s="3">
         <v>7500</v>
@@ -1392,16 +1392,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E35" s="3">
-        <v>-160000</v>
+        <v>-161600</v>
       </c>
       <c r="F35" s="3">
-        <v>-42200</v>
+        <v>-42600</v>
       </c>
       <c r="G35" s="3">
-        <v>-59700</v>
+        <v>-60300</v>
       </c>
       <c r="H35" s="3">
         <v>7500</v>
@@ -1483,7 +1483,7 @@
         <v>800</v>
       </c>
       <c r="F41" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="G41" s="3">
         <v>500</v>
@@ -1516,10 +1516,10 @@
         <v>3600</v>
       </c>
       <c r="H42" s="3">
-        <v>87800</v>
+        <v>88700</v>
       </c>
       <c r="I42" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J42" s="3">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="F45" s="3">
         <v>2400</v>
@@ -1615,19 +1615,19 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="F46" s="3">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="G46" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="H46" s="3">
-        <v>88100</v>
+        <v>88900</v>
       </c>
       <c r="I46" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J46" s="3">
         <v>1000</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="F47" s="3">
         <v>400</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>79100</v>
+        <v>79900</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>4</v>
@@ -1831,19 +1831,19 @@
         <v>300</v>
       </c>
       <c r="E54" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F54" s="3">
-        <v>90300</v>
+        <v>91200</v>
       </c>
       <c r="G54" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="H54" s="3">
-        <v>88100</v>
+        <v>88900</v>
       </c>
       <c r="I54" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J54" s="3">
         <v>1000</v>
@@ -2007,7 +2007,7 @@
         <v>1200</v>
       </c>
       <c r="J61" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K61" s="3"/>
     </row>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2130,13 +2130,13 @@
         <v>600</v>
       </c>
       <c r="F66" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G66" s="3">
         <v>200</v>
       </c>
       <c r="H66" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="I66" s="3">
         <v>1200</v>
@@ -2272,25 +2272,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-290700</v>
+        <v>-293600</v>
       </c>
       <c r="E72" s="3">
-        <v>-275400</v>
+        <v>-278100</v>
       </c>
       <c r="F72" s="3">
-        <v>-116300</v>
+        <v>-117400</v>
       </c>
       <c r="G72" s="3">
-        <v>-74100</v>
+        <v>-74800</v>
       </c>
       <c r="H72" s="3">
-        <v>-13800</v>
+        <v>-14000</v>
       </c>
       <c r="I72" s="3">
-        <v>-21300</v>
+        <v>-21500</v>
       </c>
       <c r="J72" s="3">
-        <v>-22000</v>
+        <v>-22200</v>
       </c>
       <c r="K72" s="3"/>
     </row>
@@ -2383,16 +2383,16 @@
         <v>-1600</v>
       </c>
       <c r="E76" s="3">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="F76" s="3">
-        <v>89400</v>
+        <v>90300</v>
       </c>
       <c r="G76" s="3">
         <v>3800</v>
       </c>
       <c r="H76" s="3">
-        <v>80700</v>
+        <v>81500</v>
       </c>
       <c r="I76" s="3">
         <v>-200</v>
@@ -2466,16 +2466,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E81" s="3">
-        <v>-160000</v>
+        <v>-161600</v>
       </c>
       <c r="F81" s="3">
-        <v>-42200</v>
+        <v>-42600</v>
       </c>
       <c r="G81" s="3">
-        <v>-59700</v>
+        <v>-60300</v>
       </c>
       <c r="H81" s="3">
         <v>7500</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -2674,13 +2674,13 @@
         <v>-6000</v>
       </c>
       <c r="F89" s="3">
-        <v>-7600</v>
+        <v>-7700</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
       </c>
       <c r="H89" s="3">
-        <v>-6400</v>
+        <v>-6500</v>
       </c>
       <c r="I89" s="3">
         <v>0</v>
@@ -2943,13 +2943,13 @@
         <v>1600</v>
       </c>
       <c r="F100" s="3">
-        <v>19800</v>
+        <v>20000</v>
       </c>
       <c r="G100" s="3">
         <v>600</v>
       </c>
       <c r="H100" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -2994,10 +2994,10 @@
         <v>-800</v>
       </c>
       <c r="E102" s="3">
-        <v>-5000</v>
+        <v>-5100</v>
       </c>
       <c r="F102" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G102" s="3">
         <v>300</v>
